--- a/output/pdf_financials_xlsx/RAGE.xlsx
+++ b/output/pdf_financials_xlsx/RAGE.xlsx
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.531951</v>
+        <v>-0.531951</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.224112</v>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.531951</v>
+        <v>-0.531951</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.224112</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.531951</v>
+        <v>-0.531951</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.224112</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>13.298775</v>
+        <v>-13.298775</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>-11.2056</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.531951</v>
+        <v>-0.531951</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.224112</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.531951</v>
+        <v>-0.531951</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.224112</v>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5900,7 +5900,7 @@
         <v>-0.165711</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-0.044064</v>
       </c>
     </row>
     <row r="92">
@@ -5919,46 +5919,46 @@
         <v>1.2098</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.078871</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.560143</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.535967</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.535967</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.535967</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.545034</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.955549</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.955549</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.923704</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.243223</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.691625</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.844175999999999</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.038986</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>10.098611</v>
       </c>
     </row>
     <row r="93">
@@ -9995,7 +9995,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10094,7 +10098,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11692,7 +11700,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -13482,7 +13494,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -15480,7 +15496,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -16745,7 +16765,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17034,7 +17058,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -18018,7 +18046,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -19933,7 +19965,11 @@
           <t>Reserves 2,545,034</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -83470,10 +83506,10 @@
         </is>
       </c>
       <c r="E749" s="5" t="n">
-        <v>0.531951</v>
+        <v>-0.531951</v>
       </c>
       <c r="F749" s="5" t="n">
-        <v>0.224112</v>
+        <v>-0.224112</v>
       </c>
       <c r="G749" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RAGE.xlsx
+++ b/output/pdf_financials_xlsx/RAGE.xlsx
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004335</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.045208</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.006072</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003558</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.034669</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.531951</v>
+        <v>-0.536286</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.224112</v>
+        <v>-0.224138</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.585903</v>
+        <v>-1.631111</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.545228</v>
@@ -2051,13 +2051,13 @@
         <v>-1.200858</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.502796</v>
+        <v>-0.508868</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.607094</v>
+        <v>-1.610652</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-11.708491</v>
+        <v>-11.74316</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-13.041921</v>
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.531951</v>
+        <v>-0.536286</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.224112</v>
+        <v>-0.224138</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.585903</v>
+        <v>-1.631111</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.545228</v>
@@ -2167,13 +2167,13 @@
         <v>-1.200858</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.502796</v>
+        <v>-0.508868</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.607094</v>
+        <v>-1.610652</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-11.674098</v>
+        <v>-11.708767</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-12.939656</v>
@@ -2468,19 +2468,19 @@
         <v>0.007382</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.052934</v>
+        <v>0.316133</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.591455</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.435294</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.831921</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>6.738742</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.472268</v>
@@ -2492,7 +2492,7 @@
         <v>2.646405</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.040539</v>
       </c>
     </row>
     <row r="35">
@@ -2584,19 +2584,19 @@
         <v>0.561382</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.085934</v>
+        <v>0.349133</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.591455</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.435294</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.831921</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>6.738742</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.472268</v>
@@ -2608,7 +2608,7 @@
         <v>4.050995</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.206259</v>
+        <v>0.246798</v>
       </c>
     </row>
     <row r="37">
@@ -3280,19 +3280,19 @@
         <v>0.005533</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.233659</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.595274</v>
+        <v>0.003819</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.439194</v>
+        <v>0.0039</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.837054</v>
+        <v>0.005133</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.278466</v>
+        <v>0.539724</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.278978</v>
@@ -3304,7 +3304,7 @@
         <v>0.072296</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.10101</v>
+        <v>0.060471</v>
       </c>
     </row>
     <row r="49">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -72116,7 +72116,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -80161,7 +80161,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -82892,7 +82892,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E743" s="5" t="n">

--- a/output/pdf_financials_xlsx/RAGE.xlsx
+++ b/output/pdf_financials_xlsx/RAGE.xlsx
@@ -739,43 +739,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.253742</v>
+        <v>0.255075</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.18694</v>
+        <v>0.190651</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.443414</v>
+        <v>0.457509</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.9935310000000001</v>
+        <v>1.02926</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.999373</v>
+        <v>1.097358</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.820537</v>
+        <v>0.8673650000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.6229749999999999</v>
+        <v>0.648771</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.486073</v>
+        <v>0.504699</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.486073</v>
+        <v>0.504699</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.406299</v>
+        <v>0.430316</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.383976</v>
+        <v>0.409608</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.430497</v>
+        <v>0.457856</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>4.069143</v>
+        <v>4.208164</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0.868817</v>
@@ -922,10 +922,10 @@
         <v>1.167112</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.9935310000000001</v>
+        <v>1.02926</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.999373</v>
+        <v>1.097358</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1.498538</v>
@@ -980,10 +980,10 @@
         <v>-1.167112</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.9935310000000001</v>
+        <v>-1.02926</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.999373</v>
+        <v>-1.097358</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-1.498538</v>
@@ -1564,16 +1564,16 @@
         <v>-0.531951</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.224112</v>
+        <v>-0.218984</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1.585903</v>
+        <v>-1.641935</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-3.572699</v>
+        <v>-2.723228</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-2.058125</v>
+        <v>-1.108158</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-1.498538</v>
@@ -1622,16 +1622,16 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.005128</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>0.056032</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.849471</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.949967</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.000834</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.000113</v>
@@ -6679,7 +6679,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.107652</v>
+        <v>-0.106818</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.009591000000000001</v>
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012138</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -7014,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002354</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -7219,13 +7219,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.0264</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -7246,10 +7246,10 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>3.429772</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>1.082227</v>
       </c>
     </row>
     <row r="116">
@@ -8375,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012138</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002354</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
         <v>-0.609663</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-11.660795</v>
+        <v>-11.672933</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-12.248668</v>
@@ -8444,7 +8444,7 @@
         <v>-2.778424</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-7.236677</v>
+        <v>-7.239031</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>-4.972399</v>
@@ -30285,7 +30285,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -30386,7 +30390,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -34394,7 +34402,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -34495,7 +34507,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -41159,7 +41175,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -43962,7 +43982,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -48469,7 +48493,11 @@
           <t>Private placement 2,247,777 809,200</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -49584,7 +49612,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -50998,7 +51030,11 @@
           <t>Proceeds from sale of marketable securities 26,400</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -51202,7 +51238,11 @@
           <t>Proceeds from shares issued 960,000</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -52725,7 +52765,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -58674,7 +58718,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -62140,7 +62188,11 @@
           <t>Decrease (increase) in GST receivable</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E535" s="5" t="n">
         <v>0.000834</v>
       </c>
@@ -69410,7 +69462,11 @@
           <t>Directors' fees (note 12)</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>
@@ -69994,7 +70050,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E613" t="inlineStr">
         <is>
           <t>-</t>
@@ -71459,7 +71519,11 @@
           <t>Directors' fees 13</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
           <t>-</t>
@@ -76632,7 +76696,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E681" t="inlineStr">
         <is>
           <t>-</t>
@@ -76729,7 +76797,11 @@
           <t>Loss from discontinued operations 9</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E682" t="inlineStr">
         <is>
           <t>-</t>
@@ -78337,7 +78409,11 @@
           <t>Loss from discontinued operations 11</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr">
         <is>
           <t>-</t>
@@ -79353,7 +79429,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E708" t="inlineStr">
         <is>
           <t>-</t>
@@ -80771,7 +80851,11 @@
           <t>Net loss from continuing operation</t>
         </is>
       </c>
-      <c r="D722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E722" t="inlineStr">
         <is>
           <t>-</t>
@@ -80870,7 +80954,11 @@
           <t>Net income (loss) from discontinued operation</t>
         </is>
       </c>
-      <c r="D723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E723" t="inlineStr">
         <is>
           <t>-</t>
@@ -81975,7 +82063,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E734" s="5" t="n">
         <v>0.001333</v>
       </c>
